--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.40744241561417</v>
+        <v>3.153709392537302</v>
       </c>
       <c r="D2" t="n">
-        <v>18.77431319228408</v>
+        <v>3.050825893746163</v>
       </c>
       <c r="E2" t="n">
-        <v>11.52074910149277</v>
+        <v>1.872121728992575</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8236154290373</v>
+        <v>2.083837507218562</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.77624273098177</v>
+        <v>3.051139443784537</v>
       </c>
       <c r="D3" t="n">
-        <v>44.23802833022231</v>
+        <v>7.188679603661126</v>
       </c>
       <c r="E3" t="n">
-        <v>11.52074910149277</v>
+        <v>1.872121728992575</v>
       </c>
       <c r="F3" t="n">
-        <v>12.8236154290373</v>
+        <v>2.083837507218562</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.19574958452613</v>
+        <v>3.931809307485496</v>
       </c>
       <c r="D4" t="n">
-        <v>23.88749883228405</v>
+        <v>3.881718560246157</v>
       </c>
       <c r="E4" t="n">
-        <v>11.52074910149277</v>
+        <v>1.872121728992575</v>
       </c>
       <c r="F4" t="n">
-        <v>12.8236154290373</v>
+        <v>2.083837507218562</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.95532767008537</v>
+        <v>7.630240746388872</v>
       </c>
       <c r="D5" t="n">
-        <v>48.79534507686446</v>
+        <v>7.929243574990474</v>
       </c>
       <c r="E5" t="n">
-        <v>11.52074910149277</v>
+        <v>1.872121728992575</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8236154290373</v>
+        <v>2.083837507218562</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
